--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_705_Slovenia.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_705_Slovenia.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R288e5d38fd764b3c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R1338b89f6ca04095"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R5fca6f7572c0450f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R329215ab3e1a4ebe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R37a652ede1014bea"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="Rc5ac0e04e59d4e84"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R2730b9f4408f46cc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R0fe7867a723c4b33"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Rf2c43eb26a1345af"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R526b7589c42d431d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R30a81611e73045df"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R7294f80ef0504086"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ705CommercialTable" displayName="EEZ705CommercialTable" ref="A1:O12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O12"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ705CommercialTable" displayName="EEZ705CommercialTable" ref="A1:E12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E12"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ705FunctionalTable" displayName="EEZ705FunctionalTable" ref="A1:O22" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O22"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ705FunctionalTable" displayName="EEZ705FunctionalTable" ref="A1:E22" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E22"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ705ValidationTable" displayName="EEZ705ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ705ValidationTable" displayName="EEZ705ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -6054,7 +6008,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0915f7a9bb9e4f45"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R528112d2cdcc4c4e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6064,20 +6018,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -6085,660 +6029,231 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>6.9827345882</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.1949052822100508</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>156.64094055844174</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>6.9827345882</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>156.81007965289353</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$81,A2,'Species'!$U$2:$U$81))</x:f>
-        <x:v>1094.9631669706566</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.1949052822100508</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>156.64094055844174</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>1093.7821135656113</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>1.1810534050453043</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0010797885523974</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.0010797885523975137</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Cod-likes</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>26.899342075600003</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.356226704181584</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>2271.050043515909</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>26.899342075600003</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>2274.3499658060737</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$81,A3,'Species'!$U$2:$U$81))</x:f>
-        <x:v>61178.517729846746</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.356226704181584</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>2271.050043515909</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>61089.7519913407</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>88.76573850604473</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.0014530381219853</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.0014530381219852884</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>1.5224671978</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.5751416882841958</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>375.9600409941573</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>1.5224671978</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>393.8982309538831</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$81,A4,'Species'!$U$2:$U$81))</x:f>
-        <x:v>599.6971358987356</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.5751416882841958</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>375.9600409941573</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>572.3868300971477</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>27.3103058015879</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0477130226720148</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.04771302267201482</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>14.6448625483</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.283303198410873</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>192.00087080236912</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>14.6448625483</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>284.6472308011983</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$81,A5,'Species'!$U$2:$U$81))</x:f>
-        <x:v>4168.619569837775</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.283303198410873</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>192.00087080236912</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>2811.8263620546027</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>1356.7932077831724</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.4825309365090962</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.4825309365090962</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>48.017877369299995</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.1459564075029043</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>139.9446845438068</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>48.017877369299995</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>140.54809405513163</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$81,A6,'Species'!$U$2:$U$81))</x:f>
-        <x:v>6748.821144828152</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.1459564075029043</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>139.9446845438068</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>6719.846700909888</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>28.974443918264114</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0043117715638277</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.0043117715638276224</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>2.9022656356</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>2.7214318035210243</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>52.65405266929114</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>2.9022656356</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>103.74177241150453</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$81,A7,'Species'!$U$2:$U$81))</x:f>
-        <x:v>301.0861810461457</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>2.7214318035210243</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>52.65405266929114</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>152.81604763715612</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>148.2701334089896</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.9702523766420117</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.9702523766420118</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>50.01236277040001</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.5402309716938993</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>346.9213052431263</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>50.01236277040001</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>533.3274513064504</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$81,A8,'Species'!$U$2:$U$81))</x:f>
-        <x:v>26672.965970151043</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.5402309716938993</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>346.9213052431263</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>17350.35417059991</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>9322.611799551134</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.5373153601295502</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.5373153601295503</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>45.550184333199994</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.554100417299714</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>358.17924551095746</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>45.550184333199994</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>514.473415638167</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$81,A9,'Species'!$U$2:$U$81))</x:f>
-        <x:v>23434.358916849524</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.554100417299714</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>358.17924551095746</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>16315.130657350608</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>7119.228259498916</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.436357416254673</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.43635741625467295</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>2.7830428949999995</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.9073679506359182</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>807.9192399614232</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>2.7830428949999995</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>829.4783304140668</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$81,A10,'Species'!$U$2:$U$81))</x:f>
-        <x:v>2308.4737740153305</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.9073679506359182</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>807.9192399614232</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>2248.4739005084384</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>59.99987350689207</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0266847097906382</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.026684709790638236</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>3.4685545936000004</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.7416405453140333</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>551.6206876324003</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>3.4685545936000004</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>556.3086734016827</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$H$2:$H$81,A11,'Species'!$U$2:$U$81))</x:f>
-        <x:v>1929.5870045869287</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.7416405453140333</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>551.6206876324003</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>1913.3264700121529</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>16.260534574775875</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.0084985677194298</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.008498567719429813</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>0.7373202328</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>4.349454811130743</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>2235.912537198397</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>0.7373202328</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>2424.4781156589006</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$H$2:$H$81,A12,'Species'!$U$2:$U$81))</x:f>
-        <x:v>1787.616768656126</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>4.349454811130743</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>2235.912537198397</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>1648.5835524475608</x:v>
       </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>139.03321620856514</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.0843349528764559</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.0843349528764558</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G12">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O12">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R70ee601c1a994049"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R36c6423d4cf7413f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6748,20 +6263,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -6769,1200 +6274,421 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>22.2812980733</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.8114919339003785</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>647.8760622321935</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>22.2812980733</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>789.6199225459026</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$81,A2,'Species'!$U$2:$U$81))</x:f>
-        <x:v>17593.756858861314</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.8114919339003785</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>647.8760622321935</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>14435.519657151364</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>3158.2372017099497</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.2187823699263474</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.21878236992634742</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>0.2</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>2.14</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>13.803842646028853</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>0.2</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>13.803842646028853</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$81,A3,'Species'!$U$2:$U$81))</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>2.760768529205771</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>2.14</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>13.803842646028853</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
-        <x:v>2.760768529205771</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>3.4257602246</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.820437844721072</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>661.3598783273467</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>3.4257602246</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>700.0148231207648</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$81,A4,'Species'!$U$2:$U$81))</x:f>
-        <x:v>2398.0829376775205</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.820437844721072</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>661.3598783273467</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>2265.6603653201196</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>132.4225723574009</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0584476713210678</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.058447671321067866</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large flatfishes (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>0.1000046299</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.36</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>2290.867652767775</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>0.1000046299</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>2290.867652767775</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$81,A5,'Species'!$U$2:$U$81))</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>229.09737176492305</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.36</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>2290.867652767775</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
-        <x:v>229.09737176492305</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>0.0002786134</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4.401091928816059</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>2518.209910714464</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>0.0002786134</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>2518.9540900949078</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$81,A6,'Species'!$U$2:$U$81))</x:f>
-        <x:v>0.7018143634852486</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4.401091928816059</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>2518.209910714464</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>0.7016070251378533</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>0.00020733834739528056</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0002955192008725</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.0002955192008725144</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>0.2000163901</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.8400164983479517</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>691.8572532811676</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>0.2000163901</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>691.8647679798197</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$81,A7,'Species'!$U$2:$U$81))</x:f>
-        <x:v>138.3842933286976</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.8400164983479517</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>691.8572532811676</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>138.3827902658005</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>0.001503062897086238</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.0000108616316683</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.000010861631668209687</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>0.0259904039</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.9200000000000004</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>831.7637711026717</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>0.0259904039</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>831.7637711026708</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$81,A8,'Species'!$U$2:$U$81))</x:f>
-        <x:v>21.617876360345562</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.9200000000000004</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>831.7637711026717</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>21.617876360345587</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>-2.4868995751603507e-14</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>0.9999999999999989</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>-1.1503903222067436e-15</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>3.0885382035</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.749352444467828</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>561.5034699908048</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>3.0885382035</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>561.5218589201434</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$81,A9,'Species'!$U$2:$U$81))</x:f>
-        <x:v>1734.2817133752003</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.749352444467828</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>561.5034699908048</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>1734.2249184644165</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>0.05679491078376486</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.000032749449151</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.00003274944915106766</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>0.11091837770000001</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.0042741883521074</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>100.9890271007405</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>0.11091837770000001</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>101.56702395917867</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$81,A10,'Species'!$U$2:$U$81))</x:f>
-        <x:v>11.265649525369131</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.0042741883521074</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>100.9890271007405</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>11.201539051515473</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>0.06411047385365798</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0057233629735</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.005723362973500001</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Medium bathydemersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>0.9075490266</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>4.27</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>1862.0871366628655</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>0.9075490266</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>1862.0871366628655</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$81,A11,'Species'!$U$2:$U$81))</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>1689.9353683227648</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>4.27</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>1862.0871366628655</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
-        <x:v>1689.9353683227648</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>34.1246483948</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>4.183540899427095</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>1525.9520936808576</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>34.1246483948</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>1914.4253805020433</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$81,A12,'Species'!$U$2:$U$81))</x:f>
-        <x:v>65329.092987713426</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>4.183540899427095</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>1525.9520936808576</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>52072.57866416818</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>13256.514323545249</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.254577642659883</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.2545776426598829</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>43.5955994122</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>3.4016387779452573</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>252.13827538092107</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>43.5955994122</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>308.43072712523326</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$81,A13,'Species'!$U$2:$U$81))</x:f>
-        <x:v>13446.222426165237</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>3.4016387779452573</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>252.13827538092107</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>10992.119249989604</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>2454.103176175633</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.2232602394827508</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.2232602394827507</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>5.7666928348</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>3.7323781537745933</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>539.9805958512902</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>5.7666928348</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>887.383497142852</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$81,A14,'Species'!$U$2:$U$81))</x:f>
-        <x:v>5117.268054693451</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>3.7323781537745933</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>539.9805958512902</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>3113.90223302667</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>2003.365821666781</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.6433618244075496</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.6433618244075496</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>3.7636098566</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>2.695133345351171</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>49.56023367009248</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>3.7636098566</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>79.07745874870542</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$81,A15,'Species'!$U$2:$U$81))</x:f>
-        <x:v>297.61670318150766</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>2.695133345351171</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>49.56023367009248</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>186.52538393615924</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>111.09131924534842</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.5955828472299023</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.5955828472299024</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>2.9022656356</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>2.7214318035210243</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>52.65405266929114</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>2.9022656356</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>103.74177241150453</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$81,A16,'Species'!$U$2:$U$81))</x:f>
-        <x:v>301.0861810461457</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>2.7214318035210243</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>52.65405266929114</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>152.81604763715612</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>148.2701334089896</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1.9702523766420117</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0.9702523766420118</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>1.4115488201</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>3.62</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>416.8693834703355</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>1.4115488201</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>416.8693834703355</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$81,A17,'Species'!$U$2:$U$81))</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>588.4314863733665</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>3.62</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>416.8693834703355</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
-        <x:v>588.4314863733665</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Small benthopelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>1.5097410155</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>3.64</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>436.5158322401661</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>1.5097410155</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>436.51583224016605</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$81,A18,'Species'!$U$2:$U$81))</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>659.025855848096</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>3.64</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>436.5158322401661</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
-        <x:v>659.025855848096</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>10.381084451300001</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>3.811378884029327</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>647.7074375398915</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>10.381084451300001</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>850.1858884981103</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$81,A19,'Species'!$U$2:$U$81))</x:f>
-        <x:v>8825.85150780241</x:v>
-      </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>3.811378884029327</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>647.7074375398915</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>6723.905608836735</x:v>
-      </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>2101.945898965675</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>1.3126078831629109</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>0.3126078831629108</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="18" customHeight="1">
       <x:c r="A20" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B20" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C20" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D20" s="31" t="n">
+      <x:c r="B20" s="31" t="n">
         <x:v>55.0006119575</x:v>
       </x:c>
+      <x:c r="C20" s="32" t="n">
+        <x:v>3.152170829275795</x:v>
+      </x:c>
+      <x:c r="D20" s="32" t="n">
+        <x:f>IF(C20="","",(1/'Metadata'!$B$5)^(C20-1))</x:f>
+        <x:v>141.96158162616632</x:v>
+      </x:c>
       <x:c r="E20" s="31" t="n">
-        <x:v>55.0006119575</x:v>
-      </x:c>
-      <x:c r="F20" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G20" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H20" s="32" t="n">
-        <x:f>IF(E20=0,"",I20/E20)</x:f>
-        <x:v>142.61267343461282</x:v>
-      </x:c>
-      <x:c r="I20" s="31" t="n">
-        <x:f>IF(C20=0,"",SUMIF('Species'!$G$2:$G$81,A20,'Species'!$U$2:$U$81))</x:f>
-        <x:v>7843.784311798809</x:v>
-      </x:c>
-      <x:c r="J20" s="32" t="n">
-        <x:v>3.152170829275795</x:v>
-      </x:c>
-      <x:c r="K20" s="32" t="n">
-        <x:f>IF(J20="","",(1/'Metadata'!$B$5)^(J20-1))</x:f>
-        <x:v>141.96158162616632</x:v>
-      </x:c>
-      <x:c r="L20" s="31" t="n">
-        <x:f>IF(E20=0,"",E20*K20)</x:f>
+        <x:f>IF(B20=0,"",B20*D20)</x:f>
         <x:v>7807.973863893735</x:v>
-      </x:c>
-      <x:c r="M20" s="31" t="n">
-        <x:f>IF(E20=0,"",I20-L20)</x:f>
-        <x:v>35.81044790507349</x:v>
-      </x:c>
-      <x:c r="N20" s="32" t="n">
-        <x:f>IF(L20=0,"",I20/L20)</x:f>
-        <x:v>1.004586394438469</x:v>
-      </x:c>
-      <x:c r="O20" s="34" t="n">
-        <x:f>IF(L20=0,"",M20/L20)</x:f>
-        <x:v>0.004586394438468994</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="18" customHeight="1">
       <x:c r="A21" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B21" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C21" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D21" s="31" t="n">
+      <x:c r="B21" s="31" t="n">
         <x:v>14.5448579184</x:v>
       </x:c>
+      <x:c r="C21" s="32" t="n">
+        <x:v>3.2759002615268207</x:v>
+      </x:c>
+      <x:c r="D21" s="32" t="n">
+        <x:f>IF(C21="","",(1/'Metadata'!$B$5)^(C21-1))</x:f>
+        <x:v>188.75578097323927</x:v>
+      </x:c>
       <x:c r="E21" s="31" t="n">
-        <x:v>14.5448579184</x:v>
-      </x:c>
-      <x:c r="F21" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G21" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H21" s="32" t="n">
-        <x:f>IF(E21=0,"",I21/E21)</x:f>
-        <x:v>270.8532610063624</x:v>
-      </x:c>
-      <x:c r="I21" s="31" t="n">
-        <x:f>IF(C21=0,"",SUMIF('Species'!$G$2:$G$81,A21,'Species'!$U$2:$U$81))</x:f>
-        <x:v>3939.522198072852</x:v>
-      </x:c>
-      <x:c r="J21" s="32" t="n">
-        <x:v>3.2759002615268207</x:v>
-      </x:c>
-      <x:c r="K21" s="32" t="n">
-        <x:f>IF(J21="","",(1/'Metadata'!$B$5)^(J21-1))</x:f>
-        <x:v>188.75578097323927</x:v>
-      </x:c>
-      <x:c r="L21" s="31" t="n">
-        <x:f>IF(E21=0,"",E21*K21)</x:f>
+        <x:f>IF(B21=0,"",B21*D21)</x:f>
         <x:v>2745.426015532395</x:v>
-      </x:c>
-      <x:c r="M21" s="31" t="n">
-        <x:f>IF(E21=0,"",I21-L21)</x:f>
-        <x:v>1194.096182540457</x:v>
-      </x:c>
-      <x:c r="N21" s="32" t="n">
-        <x:f>IF(L21=0,"",I21/L21)</x:f>
-        <x:v>1.4349402153927273</x:v>
-      </x:c>
-      <x:c r="O21" s="34" t="n">
-        <x:f>IF(L21=0,"",M21/L21)</x:f>
-        <x:v>0.4349402153927273</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="18" customHeight="1">
       <x:c r="A22" s="24" t="str">
         <x:v>Small to medium rays (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B22" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C22" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D22" s="31" t="n">
+      <x:c r="B22" s="31" t="n">
         <x:v>0.18</x:v>
       </x:c>
+      <x:c r="C22" s="32" t="n">
+        <x:v>3.5</x:v>
+      </x:c>
+      <x:c r="D22" s="32" t="n">
+        <x:f>IF(C22="","",(1/'Metadata'!$B$5)^(C22-1))</x:f>
+        <x:v>316.22776601683796</x:v>
+      </x:c>
       <x:c r="E22" s="31" t="n">
-        <x:v>0.18</x:v>
-      </x:c>
-      <x:c r="F22" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G22" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H22" s="32" t="n">
-        <x:f>IF(E22=0,"",I22/E22)</x:f>
-        <x:v>316.22776601683796</x:v>
-      </x:c>
-      <x:c r="I22" s="31" t="n">
-        <x:f>IF(C22=0,"",SUMIF('Species'!$G$2:$G$81,A22,'Species'!$U$2:$U$81))</x:f>
+        <x:f>IF(B22=0,"",B22*D22)</x:f>
         <x:v>56.92099788303083</x:v>
       </x:c>
-      <x:c r="J22" s="32" t="n">
-        <x:v>3.5</x:v>
-      </x:c>
-      <x:c r="K22" s="32" t="n">
-        <x:f>IF(J22="","",(1/'Metadata'!$B$5)^(J22-1))</x:f>
-        <x:v>316.22776601683796</x:v>
-      </x:c>
-      <x:c r="L22" s="31" t="n">
-        <x:f>IF(E22=0,"",E22*K22)</x:f>
-        <x:v>56.92099788303083</x:v>
-      </x:c>
-      <x:c r="M22" s="31" t="n">
-        <x:f>IF(E22=0,"",I22-L22)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N22" s="32" t="n">
-        <x:f>IF(L22=0,"",I22/L22)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O22" s="34" t="n">
-        <x:f>IF(L22=0,"",M22/L22)</x:f>
-        <x:v>0</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G22">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O22">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc030e7a3a4dc439c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R33c1287193d34ed6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8137,7 +6863,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -8236,7 +6962,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>130224.70736268716</x:v>
+        <x:v>111916.27879652377</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -8250,7 +6976,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>130224.70736268717</x:v>
+        <x:v>105628.72766938074</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -8264,7 +6990,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-18308.42856616339</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -8278,7 +7004,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>1.4551915228366852e-11</x:v>
+        <x:v>-24595.97969330642</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -8289,9 +7015,9 @@
         <x:v>EEZ_705</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -8303,47 +7029,19 @@
         <x:v>EEZ_705</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_705</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_705</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R17ea52190e874ad8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Red7ff82952654cfc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8390,7 +7088,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
